--- a/artfynd/A 7837-2024 artfynd.xlsx
+++ b/artfynd/A 7837-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137435138</v>
       </c>
       <c r="B2" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137435140</v>
       </c>
       <c r="B3" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137435162</v>
       </c>
       <c r="B4" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137435161</v>
       </c>
       <c r="B5" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137435163</v>
       </c>
       <c r="B6" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137435167</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137435171</v>
       </c>
       <c r="B8" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137435165</v>
       </c>
       <c r="B9" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137435174</v>
       </c>
       <c r="B10" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137435178</v>
       </c>
       <c r="B11" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137435176</v>
       </c>
       <c r="B12" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137435168</v>
       </c>
       <c r="B13" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137435134</v>
       </c>
       <c r="B14" t="n">
-        <v>89390</v>
+        <v>89391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>137435157</v>
       </c>
       <c r="B15" t="n">
-        <v>89390</v>
+        <v>89391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137435135</v>
       </c>
       <c r="B16" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137435177</v>
       </c>
       <c r="B17" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137435166</v>
       </c>
       <c r="B18" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>137435133</v>
       </c>
       <c r="B20" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>137435172</v>
       </c>
       <c r="B21" t="n">
-        <v>92970</v>
+        <v>92971</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137435173</v>
       </c>
       <c r="B22" t="n">
-        <v>92970</v>
+        <v>92971</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137435164</v>
       </c>
       <c r="B23" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>137435169</v>
       </c>
       <c r="B24" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>137435136</v>
       </c>
       <c r="B25" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>137435155</v>
       </c>
       <c r="B26" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137435170</v>
       </c>
       <c r="B27" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137435159</v>
       </c>
       <c r="B28" t="n">
-        <v>87617</v>
+        <v>87618</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>137435160</v>
       </c>
       <c r="B29" t="n">
-        <v>93509</v>
+        <v>93510</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 7837-2024 artfynd.xlsx
+++ b/artfynd/A 7837-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137435138</v>
       </c>
       <c r="B2" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137435140</v>
       </c>
       <c r="B3" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137435162</v>
       </c>
       <c r="B4" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137435161</v>
       </c>
       <c r="B5" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137435163</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137435167</v>
       </c>
       <c r="B7" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137435171</v>
       </c>
       <c r="B8" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137435165</v>
       </c>
       <c r="B9" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137435174</v>
       </c>
       <c r="B10" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137435178</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137435176</v>
       </c>
       <c r="B12" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137435168</v>
       </c>
       <c r="B13" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137435134</v>
       </c>
       <c r="B14" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>137435157</v>
       </c>
       <c r="B15" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137435135</v>
       </c>
       <c r="B16" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137435177</v>
       </c>
       <c r="B17" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137435166</v>
       </c>
       <c r="B18" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>137435133</v>
       </c>
       <c r="B20" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>137435172</v>
       </c>
       <c r="B21" t="n">
-        <v>92971</v>
+        <v>92974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137435173</v>
       </c>
       <c r="B22" t="n">
-        <v>92971</v>
+        <v>92974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137435164</v>
       </c>
       <c r="B23" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>137435169</v>
       </c>
       <c r="B24" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>137435136</v>
       </c>
       <c r="B25" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>137435155</v>
       </c>
       <c r="B26" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137435170</v>
       </c>
       <c r="B27" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137435159</v>
       </c>
       <c r="B28" t="n">
-        <v>87618</v>
+        <v>87621</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>137435160</v>
       </c>
       <c r="B29" t="n">
-        <v>93510</v>
+        <v>93513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 7837-2024 artfynd.xlsx
+++ b/artfynd/A 7837-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137435138</v>
       </c>
       <c r="B2" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137435140</v>
       </c>
       <c r="B3" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137435162</v>
       </c>
       <c r="B4" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137435161</v>
       </c>
       <c r="B5" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137435163</v>
       </c>
       <c r="B6" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137435167</v>
       </c>
       <c r="B7" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137435171</v>
       </c>
       <c r="B8" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137435165</v>
       </c>
       <c r="B9" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137435174</v>
       </c>
       <c r="B10" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137435178</v>
       </c>
       <c r="B11" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137435176</v>
       </c>
       <c r="B12" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137435168</v>
       </c>
       <c r="B13" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137435134</v>
       </c>
       <c r="B14" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>137435157</v>
       </c>
       <c r="B15" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137435135</v>
       </c>
       <c r="B16" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137435177</v>
       </c>
       <c r="B17" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137435166</v>
       </c>
       <c r="B18" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>137435132</v>
       </c>
       <c r="B19" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>137435133</v>
       </c>
       <c r="B20" t="n">
-        <v>107866</v>
+        <v>107872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>137435172</v>
       </c>
       <c r="B21" t="n">
-        <v>92974</v>
+        <v>92978</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137435173</v>
       </c>
       <c r="B22" t="n">
-        <v>92974</v>
+        <v>92978</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137435164</v>
       </c>
       <c r="B23" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>137435169</v>
       </c>
       <c r="B24" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>137435136</v>
       </c>
       <c r="B25" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>137435155</v>
       </c>
       <c r="B26" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137435170</v>
       </c>
       <c r="B27" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137435159</v>
       </c>
       <c r="B28" t="n">
-        <v>87621</v>
+        <v>87625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>137435160</v>
       </c>
       <c r="B29" t="n">
-        <v>93513</v>
+        <v>93517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
